--- a/scraper/output/c40_jobs.xlsx
+++ b/scraper/output/c40_jobs.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -501,6 +501,27 @@
         <v/>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Clean Construction Manager</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Climate Solutions and Networks - Brazil, Colombia</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="D4" s="2">
+        <f>HYPERLINK("https://c40.bamboohr.com/careers/706", "Clean Construction Manager")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scraper/output/c40_jobs.xlsx
+++ b/scraper/output/c40_jobs.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -483,41 +483,20 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Media and Communications Senior Manager, GCoM</t>
+          <t>Clean Construction Manager</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Global Covenant of Mayors - Brazil, South Africa</t>
+          <t>Climate Solutions and Networks - Brazil, Colombia</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="D3" s="2">
-        <f>HYPERLINK("https://c40.bamboohr.com/careers/705", "Media and Communications Senior Manager, GCoM")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Clean Construction Manager</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Climate Solutions and Networks - Brazil, Colombia</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="D4" s="2">
         <f>HYPERLINK("https://c40.bamboohr.com/careers/706", "Clean Construction Manager")</f>
         <v/>
       </c>

--- a/scraper/output/c40_jobs.xlsx
+++ b/scraper/output/c40_jobs.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -462,41 +462,20 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Senior Manager, Data System Development</t>
+          <t>Clean Construction Manager</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Business Planning, Measurement and Innovation - Brazil, Colombia, Denmark, US, UK</t>
+          <t>Climate Solutions and Networks - Brazil, Colombia</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Governance, Learning</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="D2" s="2">
-        <f>HYPERLINK("https://c40.bamboohr.com/careers/704", "Senior Manager, Data System Development")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Clean Construction Manager</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Climate Solutions and Networks - Brazil, Colombia</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="D3" s="2">
         <f>HYPERLINK("https://c40.bamboohr.com/careers/706", "Clean Construction Manager")</f>
         <v/>
       </c>

--- a/scraper/output/c40_jobs.xlsx
+++ b/scraper/output/c40_jobs.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -480,6 +480,27 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Director of Operations | C40 x GCoM Joint Program (Maternity Cover)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Business Planning, Measurement and Innovation - Brazil, UK (Hybrid)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D3" s="2">
+        <f>HYPERLINK("https://c40.bamboohr.com/careers/707", "Director of Operations | C40 x GCoM Joint Program (Maternity Cover)")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scraper/output/c40_jobs.xlsx
+++ b/scraper/output/c40_jobs.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -501,6 +501,27 @@
         <v/>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>People Manager, Special Projects (Maternity cover)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Corporate Services - South Africa, US, London, City of (Hybrid)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D4" s="2">
+        <f>HYPERLINK("https://c40.bamboohr.com/careers/708", "People Manager, Special Projects (Maternity cover)")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
